--- a/PointCloud_Project_Time_Plan_Viktor - Rough_Final.xlsx
+++ b/PointCloud_Project_Time_Plan_Viktor - Rough_Final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Desktop\Skola\Andra Kurser\D7016B - Industrial AI and eMaintenance Part 2-Practical Implementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CEC113-1CD5-4CFC-9135-6A64213BF01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF3212-33AA-40EE-B121-A0863C901F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>Project: Point Cloud Processing - Extracting Railway Track Geometry</t>
   </si>
@@ -107,9 +107,6 @@
     <t>1.1 Agree project idea and scope with supervisor</t>
   </si>
   <si>
-    <t>Understand what the common track geometry faults are, agree the scope with Amit, and have the tools and a test point cloud ready so the work can start as soon as the LTU data arrives.</t>
-  </si>
-  <si>
     <t>1.2 Submit Project Time Plan</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>2.1 Demonstration 1 + hand in Report 1 (Introduction)</t>
   </si>
   <si>
-    <t>Get from a raw point cloud to the two extracted rails and a fitted track centreline, and divide the track into fixed sections.</t>
-  </si>
-  <si>
     <t>3.1 Demonstration 2 + hand in Report 2 (Introduction + Method)</t>
   </si>
   <si>
@@ -137,15 +131,6 @@
     <t>Place the vibration events from the previous course on the same track positions, and see whether the extracted geometry says anything about why those events happened.</t>
   </si>
   <si>
-    <t>4.2 Place the vibration events on the track - by position log, or relative position if no GPS</t>
-  </si>
-  <si>
-    <t>4.3 Join the vibration features and the geometry features into one table</t>
-  </si>
-  <si>
-    <t>4.4 Analyse the relationship - correlation, and re-run the SVM model from D7015B with the geometry columns added</t>
-  </si>
-  <si>
     <t>4.5 Clean and comment the code, write the README</t>
   </si>
   <si>
@@ -200,25 +185,49 @@
     <t>3.5 Write Report 3 - Results</t>
   </si>
   <si>
-    <t>2.3 Extract the track - remove ground/track bed, then find the two rails</t>
-  </si>
-  <si>
-    <t>3.3 Build the condition table - one row per section, with a quality index (TQI)</t>
-  </si>
-  <si>
-    <t>3.2 Measure the track geometry in each section (example gage, cross-level, Surface, Twist)</t>
-  </si>
-  <si>
     <t>Apply further analysis to any correleation between abnomalies and track behaviour</t>
   </si>
   <si>
-    <t>2.4 Fit the track centreline and split the track into fixed sections (e.g. 25 m - turns 3d into 1d problem by using center line)</t>
-  </si>
-  <si>
-    <t>3.4 Plot the geometry and the TQI (track quality index) along the track</t>
-  </si>
-  <si>
     <t>CloudCompare (new tool outside vs to visualize dataset)</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Data needed could not be fetched. Timeplan is adjusted for and project adapted to data availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get from a raw point cloud to the two extracted rails and a fitted track centreline, and divide the track into fixed sections.  ---&gt; Look into Catmul-rom. </t>
+  </si>
+  <si>
+    <t>Understand what the common track geometry faults are, agree the scope with Amit, and have the tools and a test point cloud ready so the work can start as soon as the LTU data arrives. --&gt; Done but with new dataset --&gt; Meeting set on 2026-06-24</t>
+  </si>
+  <si>
+    <t>&lt;From hereon new project&gt;</t>
+  </si>
+  <si>
+    <t>2.3 Research about Catmul-rom and update report</t>
+  </si>
+  <si>
+    <t>2.4 Load data and first attempt at analyzing it</t>
+  </si>
+  <si>
+    <t>3.2 Clean the data and noise points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Create repeatable catmul-rom algorithm </t>
+  </si>
+  <si>
+    <t>3.4 Visualise this in a 3D environment - should be possible to analyze change over time using catmul-rom</t>
+  </si>
+  <si>
+    <t>4.2 Simulate over mutiple runs</t>
+  </si>
+  <si>
+    <t>4.3 Analyze change over time</t>
+  </si>
+  <si>
+    <t>4.4 Explorative study - suggest how future studies could build upon this and these findings</t>
   </si>
 </sst>
 </file>
@@ -384,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -442,13 +451,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -460,6 +472,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,231 +736,232 @@
     <col min="3" max="3" width="55.88671875" customWidth="1"/>
     <col min="4" max="4" width="25.44140625" customWidth="1"/>
     <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.21875" customWidth="1"/>
     <col min="13" max="13" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
     </row>
     <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
     </row>
     <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="I5" s="37" t="s">
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="I5" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
       <c r="P5" s="25"/>
     </row>
     <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="30" t="s">
+      <c r="C6" s="35"/>
+      <c r="D6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="I6" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="I6" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
       <c r="P6" s="22"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="32"/>
+      <c r="D7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
       <c r="P7" s="22"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
       <c r="P8" s="22"/>
     </row>
     <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
       <c r="P9" s="22"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>46273</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="37"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
     </row>
     <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="D12" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>46325</v>
       </c>
-      <c r="D13" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
+      <c r="D13" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B15" s="9"/>
@@ -961,22 +977,22 @@
       <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="16"/>
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="6"/>
@@ -995,6 +1011,9 @@
       <c r="G19" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="H19" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="I19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1019,20 +1038,20 @@
       <c r="G20" s="20">
         <v>46274</v>
       </c>
-      <c r="I20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
+      <c r="I20" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="11">
         <v>1</v>
@@ -1047,18 +1066,18 @@
       <c r="G21" s="19">
         <v>46275</v>
       </c>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
     </row>
     <row r="22" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
       <c r="C22" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="11">
         <v>0.75</v>
@@ -1073,18 +1092,18 @@
       <c r="G22" s="27">
         <v>46282</v>
       </c>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
     </row>
     <row r="23" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
       <c r="C23" s="23" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D23" s="11">
         <v>0.5</v>
@@ -1099,18 +1118,18 @@
       <c r="G23" s="19">
         <v>46282</v>
       </c>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="11">
         <v>0.75</v>
@@ -1125,18 +1144,18 @@
       <c r="G24" s="28">
         <v>46283</v>
       </c>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="5"/>
       <c r="C25" s="23" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D25" s="11">
         <v>0</v>
@@ -1151,13 +1170,13 @@
       <c r="G25" s="19">
         <v>46283</v>
       </c>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="7"/>
@@ -1172,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="11">
         <v>0</v>
@@ -1187,23 +1206,26 @@
       <c r="G27" s="20">
         <v>46283</v>
       </c>
-      <c r="I27" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
+      <c r="H27" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
     </row>
     <row r="28" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
       <c r="C28" s="23" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D28" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E28" s="1">
         <f>G28-F28+1</f>
@@ -1215,21 +1237,22 @@
       <c r="G28" s="19">
         <v>46288</v>
       </c>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-    </row>
-    <row r="29" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H28" s="40"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="5"/>
       <c r="C29" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E29" s="1">
         <f>G29-F29+1</f>
@@ -1241,21 +1264,24 @@
       <c r="G29" s="19">
         <v>46293</v>
       </c>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-    </row>
-    <row r="30" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H29" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B30" s="5"/>
       <c r="C30" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D30" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="1">
         <f>G30-F30+1</f>
@@ -1267,18 +1293,19 @@
       <c r="G30" s="19">
         <v>46296</v>
       </c>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B31" s="5"/>
       <c r="C31" s="17" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D31" s="11">
         <v>0</v>
@@ -1293,13 +1320,14 @@
       <c r="G31" s="19">
         <v>46297</v>
       </c>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
@@ -1314,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="11">
         <v>0</v>
@@ -1329,20 +1357,20 @@
       <c r="G33" s="20">
         <v>46297</v>
       </c>
-      <c r="I33" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-    </row>
-    <row r="34" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I33" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B34" s="5"/>
       <c r="C34" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D34" s="11">
         <v>0</v>
@@ -1357,18 +1385,18 @@
       <c r="G34" s="19">
         <v>46305</v>
       </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-    </row>
-    <row r="35" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B35" s="5"/>
-      <c r="C35" s="17" t="s">
-        <v>56</v>
+      <c r="C35" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="D35" s="11">
         <v>0</v>
@@ -1383,18 +1411,18 @@
       <c r="G35" s="19">
         <v>46309</v>
       </c>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
     </row>
     <row r="36" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D36" s="11">
         <v>0</v>
@@ -1409,18 +1437,18 @@
       <c r="G36" s="19">
         <v>46310</v>
       </c>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B37" s="5"/>
       <c r="C37" s="17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D37" s="11">
         <v>0</v>
@@ -1435,13 +1463,13 @@
       <c r="G37" s="19">
         <v>46311</v>
       </c>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
@@ -1456,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" s="11">
         <v>0</v>
@@ -1471,20 +1499,20 @@
       <c r="G39" s="20">
         <v>46311</v>
       </c>
-      <c r="I39" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-    </row>
-    <row r="40" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I39" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B40" s="5"/>
-      <c r="C40" s="17" t="s">
-        <v>34</v>
+      <c r="C40" s="23" t="s">
+        <v>62</v>
       </c>
       <c r="D40" s="11">
         <v>0</v>
@@ -1499,18 +1527,18 @@
       <c r="G40" s="19">
         <v>46317</v>
       </c>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-    </row>
-    <row r="41" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B41" s="5"/>
-      <c r="C41" s="17" t="s">
-        <v>35</v>
+      <c r="C41" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="D41" s="11">
         <v>0</v>
@@ -1525,18 +1553,18 @@
       <c r="G41" s="19">
         <v>46318</v>
       </c>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
     </row>
     <row r="42" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B42" s="5"/>
-      <c r="C42" s="17" t="s">
-        <v>36</v>
+      <c r="C42" s="23" t="s">
+        <v>64</v>
       </c>
       <c r="D42" s="11">
         <v>0</v>
@@ -1551,18 +1579,18 @@
       <c r="G42" s="19">
         <v>46321</v>
       </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B43" s="5"/>
-      <c r="C43" s="17" t="s">
-        <v>37</v>
+      <c r="C43" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="D43" s="11">
         <v>0</v>
@@ -1577,18 +1605,18 @@
       <c r="G43" s="19">
         <v>46321</v>
       </c>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B44" s="5"/>
       <c r="C44" s="17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D44" s="11">
         <v>0</v>
@@ -1603,13 +1631,13 @@
       <c r="G44" s="19">
         <v>46322</v>
       </c>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
@@ -1624,7 +1652,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D46" s="11">
         <v>0</v>
@@ -1639,15 +1667,15 @@
       <c r="G46" s="20">
         <v>46323</v>
       </c>
-      <c r="I46" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
+      <c r="I46" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
@@ -1662,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D48" s="11">
         <v>0</v>
@@ -1677,20 +1705,20 @@
       <c r="G48" s="19">
         <v>46321</v>
       </c>
-      <c r="I48" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
+      <c r="I48" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B49" s="5"/>
       <c r="C49" s="17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D49" s="11">
         <v>0</v>
@@ -1705,18 +1733,18 @@
       <c r="G49" s="19">
         <v>46323</v>
       </c>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B50" s="5"/>
       <c r="C50" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D50" s="11">
         <v>0</v>
@@ -1731,18 +1759,18 @@
       <c r="G50" s="20">
         <v>46323</v>
       </c>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B51" s="5"/>
       <c r="C51" s="17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D51" s="11">
         <v>0</v>
@@ -1757,36 +1785,32 @@
       <c r="G51" s="20">
         <v>46325</v>
       </c>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="31"/>
-      <c r="M51" s="31"/>
-      <c r="N51" s="31"/>
-      <c r="O51" s="31"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C53" s="14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C54" s="15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C55" s="26" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="I27:O31"/>
-    <mergeCell ref="I33:O37"/>
-    <mergeCell ref="I39:O44"/>
-    <mergeCell ref="I46:O46"/>
-    <mergeCell ref="I48:O51"/>
+  <mergeCells count="22">
+    <mergeCell ref="H27:H28"/>
     <mergeCell ref="A1:P3"/>
     <mergeCell ref="D16:G17"/>
     <mergeCell ref="I20:O25"/>
@@ -1803,6 +1827,11 @@
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D10:G10"/>
+    <mergeCell ref="I27:O31"/>
+    <mergeCell ref="I33:O37"/>
+    <mergeCell ref="I39:O44"/>
+    <mergeCell ref="I46:O46"/>
+    <mergeCell ref="I48:O51"/>
   </mergeCells>
   <conditionalFormatting sqref="D20:D51">
     <cfRule type="dataBar" priority="3">
